--- a/curriculum-generator-kb/data/final_master_industry_skills_dataset.xlsx
+++ b/curriculum-generator-kb/data/final_master_industry_skills_dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\new data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainers\curriculum-generator-kb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029C5B66-BEB0-4C3D-A0F9-AE336EAFABA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6403FE4F-0F25-48AA-BA62-8A68842689D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read_Me &amp; Methodology" sheetId="1" r:id="rId1"/>
@@ -2597,7 +2597,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2627,6 +2627,14 @@
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2658,10 +2666,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2678,8 +2687,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7460,7 +7471,7 @@
       <c r="I11" t="s">
         <v>700</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="8" t="s">
         <v>701</v>
       </c>
       <c r="K11" t="s">
@@ -9294,6 +9305,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J11" r:id="rId1" xr:uid="{4AC440F4-66C2-43CC-B565-A59F1FB67302}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>